--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23527-2023 artfynd.xlsx
+++ b/artfynd/A 23527-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048335</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136048334</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
